--- a/Lewitus_etal_2014/pbio.1002000.s014.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s014.xlsx
@@ -2569,8 +2569,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -2594,8 +2594,6 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2670,16 +2668,6 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2823,17 +2811,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C573D47-6997-49C7-90CC-73CF66448ABB}">
   <ds:schemaRefs>
@@ -2843,9 +2820,20 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67C510A9-4E6F-4BF3-8F37-5C9C654124CD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{220F5B33-3FBB-44CD-ACB5-421856CE306F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73CD1619-5447-4119-9ECF-711B762BD938}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>